--- a/SampleFiles/DB_Employees.xlsx
+++ b/SampleFiles/DB_Employees.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Banu\2026\DotNet\SampleFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" url="C:\Banu\2026\DotNet\SampleFiles\"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F073F1-F922-4464-A609-86E6376E5826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Excel_Destination" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" r:id="rId1" name="Sheet1"/>
+    <sheet sheetId="2" r:id="rId2" name="Excel_Destination"/>
   </sheets>
   <definedNames>
-    <definedName name="Excel_Destination">Excel_Destination!$A$1:$O$10</definedName>
+    <definedName name="Excel_Destination">'Excel_Destination'!$A$1:$O$19</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -689,15 +685,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="13" width="11.7109375" customWidth="1"/>
     <col min="14" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -744,7 +740,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -791,7 +787,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -835,7 +831,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="4">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -882,7 +878,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="5">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -929,7 +925,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="6">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -973,7 +969,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="7">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -1017,7 +1013,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="8">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -1061,7 +1057,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="9">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -1108,7 +1104,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row spans="1:15" x14ac:dyDescent="0.25" outlineLevel="0" r="10">
       <c r="A10" t="s">
         <v>102</v>
       </c>
@@ -1150,6 +1146,676 @@
       </c>
       <c r="O10" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Davolio</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>1948-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>1992-05-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>507 - 20th Ave. E.Apt. 2A</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>98122</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t>(206) 555-9857</t>
+        </is>
+      </c>
+      <c r="N11" s="0" t="inlineStr">
+        <is>
+          <t>5467</t>
+        </is>
+      </c>
+      <c r="O11" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Fuller</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Vice President, Sales</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>1952-02-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>1992-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>908 W. Capital Way</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>Tacoma</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>98401</t>
+        </is>
+      </c>
+      <c r="L12" s="0" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t>(206) 555-9482</t>
+        </is>
+      </c>
+      <c r="N12" s="0" t="inlineStr">
+        <is>
+          <t>3457</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Leverling</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Janet</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>1963-08-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>1992-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>722 Moss Bay Blvd.</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>Kirkland</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>98033</t>
+        </is>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>(206) 555-3412</t>
+        </is>
+      </c>
+      <c r="N13" s="0" t="inlineStr">
+        <is>
+          <t>3355</t>
+        </is>
+      </c>
+      <c r="O13" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Peacock</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Margaret</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Mrs.</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>1937-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>1993-05-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>4110 Old Redmond Rd.</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>Redmond</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>98052</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t>(206) 555-8122</t>
+        </is>
+      </c>
+      <c r="N14" s="0" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="O14" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Buchanan</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Steven</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>1955-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>1993-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>14 Garrett Hill</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>SW1 8JR</t>
+        </is>
+      </c>
+      <c r="L15" s="0" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t>(71) 555-4848</t>
+        </is>
+      </c>
+      <c r="N15" s="0" t="inlineStr">
+        <is>
+          <t>3453</t>
+        </is>
+      </c>
+      <c r="O15" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Suyama</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>1963-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>1993-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>Coventry House_x000d_
+Miner Rd.</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>EC2 7JR</t>
+        </is>
+      </c>
+      <c r="L16" s="0" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="M16" s="0" t="inlineStr">
+        <is>
+          <t>(71) 555-7773</t>
+        </is>
+      </c>
+      <c r="N16" s="0" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="O16" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>King</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>1960-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>1994-01-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>Edgeham Hollow_x000d_
+Winchester Way</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>RG1 9SP</t>
+        </is>
+      </c>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="M17" s="0" t="inlineStr">
+        <is>
+          <t>(71) 555-5598</t>
+        </is>
+      </c>
+      <c r="N17" s="0" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="O17" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Callahan</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Inside Sales Coordinator</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>1958-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>1994-03-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>4726 - 11th Ave. N.E.</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>98105</t>
+        </is>
+      </c>
+      <c r="L18" s="0" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="M18" s="0" t="inlineStr">
+        <is>
+          <t>(206) 555-1189</t>
+        </is>
+      </c>
+      <c r="N18" s="0" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="O18" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Dodsworth</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Anne</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>1966-01-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>1994-11-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>7 Houndstooth Rd.</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>WG2 7LT</t>
+        </is>
+      </c>
+      <c r="L19" s="0" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="M19" s="0" t="inlineStr">
+        <is>
+          <t>(71) 555-4444</t>
+        </is>
+      </c>
+      <c r="N19" s="0" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="O19" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
     </row>
   </sheetData>
